--- a/Data/Modelo_KPIs - Automatizaciones con IA.xlsx
+++ b/Data/Modelo_KPIs - Automatizaciones con IA.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="KPIs" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Hoja 1" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Formato Locker" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -420,7 +420,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -439,12 +439,13 @@
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="15.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -478,6 +479,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
@@ -499,7 +505,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -578,20 +584,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -613,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -627,23 +619,23 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="2" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
@@ -657,7 +649,6 @@
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="1" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -668,16 +659,16 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -692,44 +683,44 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -738,31 +729,31 @@
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -771,7 +762,7 @@
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="12" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="11" fillId="0" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -889,22 +880,22 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style">
+    <tableStyle count="3" pivot="0" name="Formato Locker-style">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 2">
+    <tableStyle count="3" pivot="0" name="Formato Locker-style 2">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 3">
+    <tableStyle count="3" pivot="0" name="Formato Locker-style 3">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 4">
+    <tableStyle count="3" pivot="0" name="Formato Locker-style 4">
       <tableStyleElement dxfId="1" type="headerRow"/>
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
@@ -1078,7 +1069,7 @@
     <tableColumn name="Operativos  / año" id="1"/>
     <tableColumn name="Datos operativos" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Formato Locker-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1088,7 +1079,7 @@
     <tableColumn name="Adopción " id="1"/>
     <tableColumn name="Datos adopcion" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Formato Locker-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1098,7 +1089,7 @@
     <tableColumn name="Riesgo y cumplimiento" id="1"/>
     <tableColumn name="Datos riesgo" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Formato Locker-style 4" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1180,7 +1171,7 @@
     <tableColumn name="Económicos " id="1"/>
     <tableColumn name="Datos" id="2"/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Formato Locker-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -1422,7 +1413,7 @@
         <v>20384</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18.0" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1430,60 +1421,63 @@
         <f>sum(B72:B74)</f>
         <v>23920</v>
       </c>
+      <c r="D4" s="7" t="str">
+        <f>"ROI "&amp;TEXT(KPIs!$B$78,"0%")&amp;" — por cada 1 € invertido, recupera "&amp;TEXT(0+KPIs!$B$78,"0.00")&amp;" €."</f>
+        <v>ROI 17% — por cada 1 € invertido, recupera 0,17 €.</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8">
-        <f>B79</f>
-        <v>0.2458286986</v>
+      <c r="B5" s="9">
+        <f>B75</f>
+        <v>3536</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="13"/>
+      <c r="C7" s="14"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="15" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="6">
         <f>B90</f>
         <v>560</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="15"/>
+      <c r="C8" s="14"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="15" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="16">
         <f>B88</f>
         <v>7680</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C9" s="14"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="6">
         <f>B87</f>
         <v>9600</v>
       </c>
-      <c r="C10" s="13"/>
+      <c r="C10" s="14"/>
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
@@ -1493,12 +1487,12 @@
         <f>B92</f>
         <v>128</v>
       </c>
-      <c r="C11" s="13"/>
+      <c r="C11" s="14"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="13"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="14"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="19" t="s">
@@ -1507,7 +1501,7 @@
       <c r="B13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="13"/>
+      <c r="C13" s="14"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="20" t="s">
@@ -1517,7 +1511,7 @@
         <f>B49</f>
         <v>80</v>
       </c>
-      <c r="C14" s="13"/>
+      <c r="C14" s="14"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
@@ -1527,7 +1521,7 @@
         <f>B41</f>
         <v>40</v>
       </c>
-      <c r="C15" s="13"/>
+      <c r="C15" s="14"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
@@ -1537,25 +1531,25 @@
         <f>B34</f>
         <v>20</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="10"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="11"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="9">
         <f>B97</f>
         <v>192</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="10"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="19" t="s">
@@ -1564,31 +1558,31 @@
       <c r="B19" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="10"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="11"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <f>B100</f>
         <v>98</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="24" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="6">
         <f t="shared" ref="B21:B23" si="1">B98</f>
         <v>144</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="10"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
@@ -1598,492 +1592,492 @@
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="10"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="9">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="10"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="26" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="28">
         <v>10000.0</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="30" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="29">
+      <c r="B30" s="28">
         <v>30.0</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="27" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="31">
         <v>200.0</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="28"/>
+      <c r="D31" s="27"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>18.0</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="32">
         <v>5.0</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="30" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="32">
         <v>20.0</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="31" t="s">
+      <c r="D34" s="30" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1"/>
     <row r="36" ht="24.75" customHeight="1">
-      <c r="A36" s="31" t="s">
+      <c r="A36" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="33">
         <f>B34*0.1</f>
         <v>2</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="30" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="37" ht="39.0" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="34">
         <f>B34*B33/60</f>
         <v>1.666666667</v>
       </c>
-      <c r="C37" s="28" t="s">
+      <c r="C37" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="31" t="s">
+      <c r="A38" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="34">
+      <c r="B38" s="33">
         <f>B33*B34*B31/60</f>
         <v>333.3333333</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="31"/>
+      <c r="D38" s="30"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="31" t="s">
+      <c r="A39" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="B39" s="34">
+      <c r="B39" s="33">
         <f>B38*B32</f>
         <v>6000</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="31"/>
+      <c r="D39" s="30"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="B40" s="36"/>
+      <c r="B40" s="35"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="33">
+      <c r="B41" s="32">
         <v>40.0</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C41" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="D41" s="36" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="31" t="s">
+      <c r="A42" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="33">
+      <c r="B42" s="32">
         <v>50.0</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="D42" s="31" t="s">
+      <c r="D42" s="30" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="31" t="s">
+      <c r="A43" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="33">
+      <c r="B43" s="32">
         <v>80.0</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C43" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="30" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="28" t="s">
+      <c r="A44" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="28">
         <v>150.0</v>
       </c>
-      <c r="C44" s="28" t="s">
+      <c r="C44" s="27" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="28">
         <v>6000.0</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C45" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="D45" s="31" t="s">
+      <c r="D45" s="30" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="28">
         <v>2000.0</v>
       </c>
-      <c r="C46" s="28" t="s">
+      <c r="C46" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="D46" s="31" t="s">
+      <c r="D46" s="30" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="31" t="s">
+      <c r="A47" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="33">
+      <c r="B47" s="32">
         <v>0.04</v>
       </c>
-      <c r="C47" s="31" t="s">
+      <c r="C47" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="D47" s="31" t="s">
+      <c r="D47" s="30" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="31" t="s">
+      <c r="A49" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="B49" s="38">
+      <c r="B49" s="37">
         <f>B31*B41%</f>
         <v>80</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="30" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="28" t="s">
+      <c r="A50" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B50" s="35">
+      <c r="B50" s="34">
         <f>B44*B49</f>
         <v>12000</v>
       </c>
-      <c r="C50" s="28" t="s">
+      <c r="C50" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="D50" s="31" t="s">
+      <c r="D50" s="30" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="31" t="s">
+      <c r="A51" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="38">
+      <c r="B51" s="37">
         <f>B34*B42%</f>
         <v>10</v>
       </c>
-      <c r="C51" s="31" t="s">
+      <c r="C51" s="30" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="31" t="s">
+      <c r="A52" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="38">
+      <c r="B52" s="37">
         <f>B51*B49</f>
         <v>800</v>
       </c>
-      <c r="C52" s="31" t="s">
+      <c r="C52" s="30" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="31" t="s">
+      <c r="A53" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="34">
+      <c r="B53" s="33">
         <f>B36*B43%</f>
         <v>1.6</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="C53" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="D53" s="31"/>
+      <c r="D53" s="30"/>
     </row>
     <row r="54" ht="15.75" customHeight="1"/>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="31" t="s">
+      <c r="A55" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="33">
+      <c r="B55" s="32">
         <v>70.0</v>
       </c>
-      <c r="C55" s="31" t="s">
+      <c r="C55" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D55" s="31" t="s">
+      <c r="D55" s="30" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="31" t="s">
+      <c r="A56" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="B56" s="33">
+      <c r="B56" s="32">
         <v>0.6</v>
       </c>
-      <c r="C56" s="31" t="s">
+      <c r="C56" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D56" s="31"/>
+      <c r="D56" s="30"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="31" t="s">
+      <c r="A57" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="B57" s="34">
+      <c r="B57" s="33">
         <f>B33*B55%</f>
         <v>3.5</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="30" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="31" t="s">
+      <c r="A58" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="B58" s="34">
+      <c r="B58" s="33">
         <f>B34*(B33-B57)*B42%*B41%</f>
         <v>6</v>
       </c>
-      <c r="C58" s="31" t="s">
+      <c r="C58" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="D58" s="31"/>
+      <c r="D58" s="30"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="31" t="s">
+      <c r="A59" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="B59" s="34">
+      <c r="B59" s="33">
         <f>(B51*B33)-B58</f>
         <v>44</v>
       </c>
-      <c r="C59" s="31" t="s">
+      <c r="C59" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="D59" s="31"/>
+      <c r="D59" s="30"/>
     </row>
     <row r="60" ht="15.75" customHeight="1"/>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="31" t="s">
+      <c r="A61" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="B61" s="33">
+      <c r="B61" s="32">
         <v>85.0</v>
       </c>
-      <c r="C61" s="31" t="s">
+      <c r="C61" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="D61" s="31" t="s">
+      <c r="D61" s="30" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="31" t="s">
+      <c r="A62" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="B62" s="33">
+      <c r="B62" s="32">
         <v>70.0</v>
       </c>
-      <c r="C62" s="31" t="s">
+      <c r="C62" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="D62" s="31" t="s">
+      <c r="D62" s="30" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="31" t="s">
+      <c r="A63" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B63" s="33">
+      <c r="B63" s="32">
         <f>B52*1.5%</f>
         <v>12</v>
       </c>
-      <c r="C63" s="31" t="s">
+      <c r="C63" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="D63" s="31" t="s">
+      <c r="D63" s="30" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="31" t="s">
+      <c r="A64" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B64" s="33">
+      <c r="B64" s="32">
         <f>B52*2%</f>
         <v>16</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="D64" s="31" t="s">
+      <c r="D64" s="30" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="31" t="s">
+      <c r="A65" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="B65" s="33">
+      <c r="B65" s="32">
         <v>95.0</v>
       </c>
-      <c r="C65" s="31" t="s">
+      <c r="C65" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="D65" s="30" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2091,256 +2085,256 @@
     <row r="67" ht="15.75" customHeight="1"/>
     <row r="68" ht="15.75" customHeight="1"/>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="10"/>
+      <c r="A69" s="11"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="10"/>
+      <c r="A70" s="11"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="39" t="s">
+      <c r="A71" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="B71" s="39" t="s">
+      <c r="B71" s="38" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="40" t="s">
+      <c r="A72" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="B72" s="40">
+      <c r="B72" s="39">
         <f>B90*B32</f>
         <v>10080</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="39" t="s">
         <v>116</v>
       </c>
-      <c r="B73" s="41">
+      <c r="B73" s="40">
         <f>B30*B92</f>
         <v>3840</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="40" t="s">
+      <c r="A74" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="B74" s="36">
+      <c r="B74" s="35">
         <f>B29</f>
         <v>10000</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="41" t="s">
+      <c r="A75" s="40" t="s">
         <v>118</v>
       </c>
-      <c r="B75" s="36">
+      <c r="B75" s="35">
         <f>SUM(B72:B74)-B76</f>
         <v>3536</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="36">
+      <c r="B76" s="35">
         <f>B50+B45+B46+B87*B47</f>
         <v>20384</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="40" t="s">
+      <c r="A77" s="39" t="s">
         <v>120</v>
       </c>
-      <c r="B77" s="36">
+      <c r="B77" s="35">
         <f>B50+B46+B87*B47</f>
         <v>14384</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="40" t="s">
+      <c r="A78" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="B78" s="42">
+      <c r="B78" s="41">
         <f>B75/B76</f>
         <v>0.1734693878</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="40" t="s">
+      <c r="A79" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="B79" s="42">
+      <c r="B79" s="41">
         <f>B75/B77</f>
         <v>0.2458286986</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="43" t="str">
-        <f>"ROI "&amp;TEXT(KPIs!$B$78,"0%")&amp;" — por cada 1 € invertido, recuperas "&amp;TEXT(0+KPIs!$B$78,"0.00")&amp;" €."</f>
-        <v>ROI 17% — por cada 1 € invertido, recuperas 0,17 €.</v>
+      <c r="A80" s="42" t="str">
+        <f>"ROI "&amp;TEXT(KPIs!$B$78,"0%")&amp;" — por cada 1 € invertido, recupera "&amp;TEXT(0+KPIs!$B$78,"0.00")&amp;" €."</f>
+        <v>ROI 17% — por cada 1 € invertido, recupera 0,17 €.</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="43"/>
-      <c r="B81" s="43"/>
-      <c r="C81" s="43"/>
-      <c r="D81" s="43"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="43"/>
+      <c r="A81" s="42"/>
+      <c r="B81" s="42"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="43"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="43"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="43"/>
+      <c r="A82" s="42"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="10"/>
+      <c r="A83" s="11"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="44" t="s">
+      <c r="A84" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="B84" s="45" t="s">
+      <c r="B84" s="44" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="46" t="s">
+      <c r="A85" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="B85" s="47">
+      <c r="B85" s="46">
         <f>B49</f>
         <v>80</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="48" t="s">
+      <c r="A86" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="B86" s="49">
+      <c r="B86" s="48">
         <f>B34*12*B85</f>
         <v>19200</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="50" t="s">
+      <c r="A87" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="B87" s="49">
+      <c r="B87" s="48">
         <f t="shared" ref="B87:B88" si="2">B86*B42%</f>
         <v>9600</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="48" t="s">
+      <c r="A88" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="B88" s="49">
+      <c r="B88" s="48">
         <f t="shared" si="2"/>
         <v>7680</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="48" t="s">
+      <c r="A89" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="B89" s="49">
+      <c r="B89" s="48">
         <f>B37*B85*12*B42%</f>
         <v>800</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="50" t="s">
+      <c r="A90" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="B90" s="49">
+      <c r="B90" s="48">
         <f>B89*B55%</f>
         <v>560</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="51" t="s">
+      <c r="A91" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="B91" s="52">
+      <c r="B91" s="51">
         <f>B85*B36</f>
         <v>160</v>
       </c>
-      <c r="C91" s="53"/>
-      <c r="D91" s="54"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="53"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="55" t="s">
+      <c r="A92" s="54" t="s">
         <v>130</v>
       </c>
-      <c r="B92" s="56">
+      <c r="B92" s="55">
         <f>B91*B43%</f>
         <v>128</v>
       </c>
-      <c r="C92" s="54"/>
-      <c r="D92" s="54"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="C93" s="54"/>
-      <c r="D93" s="54"/>
+      <c r="C93" s="53"/>
+      <c r="D93" s="53"/>
     </row>
     <row r="94" ht="15.75" customHeight="1"/>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="57" t="s">
+      <c r="A95" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="B95" s="58" t="s">
+      <c r="B95" s="57" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="59" t="s">
+      <c r="A96" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="B96" s="60">
+      <c r="B96" s="59">
         <f>B87*B65%</f>
         <v>9120</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="59" t="s">
+      <c r="A97" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B97" s="60">
+      <c r="B97" s="59">
         <f>B64*12</f>
         <v>192</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="61" t="s">
+      <c r="A98" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="B98" s="60">
+      <c r="B98" s="59">
         <f>B63*12</f>
         <v>144</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="59" t="s">
+      <c r="A99" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="B99" s="60">
+      <c r="B99" s="59">
         <f>B62</f>
         <v>70</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="62" t="s">
+      <c r="A100" s="61" t="s">
         <v>20</v>
       </c>
-      <c r="B100" s="63">
+      <c r="B100" s="62">
         <f>(B87-B97)/B87*100</f>
         <v>98</v>
       </c>
@@ -3260,10 +3254,10 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E1" s="19" t="s">
@@ -3287,7 +3281,7 @@
         <f>KPIs!$B$78</f>
         <v>0.1734693878</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="6">
@@ -3304,7 +3298,7 @@
       <c r="G2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="23">
         <f>KPIs!B100</f>
         <v>98</v>
       </c>
@@ -3317,7 +3311,7 @@
         <f>KPIs!B76</f>
         <v>20384</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="15" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="16">
@@ -3331,7 +3325,7 @@
         <f>KPIs!B41</f>
         <v>40</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="G3" s="24" t="s">
         <v>21</v>
       </c>
       <c r="H3" s="6">
@@ -3347,7 +3341,7 @@
         <f>SUM(KPIs!B72:B74)</f>
         <v>23920</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="15" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="6">
@@ -3370,12 +3364,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8">
-        <f>KPIs!B79</f>
-        <v>0.2458286986</v>
+      <c r="B5" s="9">
+        <f>KPIs!B75</f>
+        <v>3536</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>11</v>
@@ -3387,29 +3381,29 @@
       <c r="E5" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="9">
         <f>KPIs!B97</f>
         <v>192</v>
       </c>
       <c r="G5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="9">
         <f>KPIs!B100</f>
         <v>98</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
     </row>
     <row r="12">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
     </row>
     <row r="18">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
